--- a/data/sample_bids/BoQ_PriceSchedule_MegaTech.xlsx
+++ b/data/sample_bids/BoQ_PriceSchedule_MegaTech.xlsx
@@ -463,92 +463,60 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>Vendor Name: MegaTech Solutions India Pvt Ltd</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GSTIN: 27AAACM1234F1Z5</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>GSTIN: 07AAACM9988K1ZO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PAN: AAACM1234F</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>PAN: AAACM9988K</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>EMD Bank Guarantee: INR 1,00,000 Submitted</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>Turnover: INR 12.40 Crore (Average of 3 Years)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>Warranty: 3-Year Comprehensive Warranty</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>Local Content: 55% Class-1 Local Supplier Declaration</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>Total Financial Quote: INR 48,00,000</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
